--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace2\luban_examples\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57E1AAA0-A88D-4E41-AC05-256E9DB382D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575BD8E7-9221-4578-947B-8DB8C397A7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
   <si>
     <t>##var</t>
   </si>
@@ -77,13 +77,112 @@
   </si>
   <si>
     <t>注释</t>
+  </si>
+  <si>
+    <t>生命值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>能量值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义属性3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Energy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.AttributeId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>属性类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CustomGauge01</t>
+  </si>
+  <si>
+    <t>CustomGauge02</t>
+  </si>
+  <si>
+    <t>CustomGauge03</t>
+  </si>
+  <si>
+    <t>HP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.HitEffectType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Damage</t>
+  </si>
+  <si>
+    <t>ModifyAttribute</t>
+  </si>
+  <si>
+    <t>ApplyBuff</t>
+  </si>
+  <si>
+    <t>ZZZ.EffectTarget</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Victim</t>
+  </si>
+  <si>
+    <t>Attacker</t>
+  </si>
+  <si>
+    <t>ZZZ.EffectTriggerPolicy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EveryHit</t>
+  </si>
+  <si>
+    <t>FirstHitOnly</t>
+  </si>
+  <si>
+    <t>造成伤害</t>
+  </si>
+  <si>
+    <t>修改属性(如回血/回能)</t>
+  </si>
+  <si>
+    <t>施加Buff</t>
+  </si>
+  <si>
+    <t>受击者</t>
+  </si>
+  <si>
+    <t>攻击者自身</t>
+  </si>
+  <si>
+    <t>每次命中触发</t>
+  </si>
+  <si>
+    <t>仅首次命中触发</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,8 +193,23 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -141,7 +255,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -151,8 +265,14 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -429,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -465,13 +585,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -528,6 +648,153 @@
         <v>18</v>
       </c>
       <c r="L3" s="1"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4">
+        <v>100</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J5">
+        <v>200</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>1000</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J7">
+        <v>1100</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8">
+        <v>1200</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" t="s">
+        <v>33</v>
+      </c>
+      <c r="J10">
+        <v>2</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>36</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" t="s">
+        <v>39</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{575BD8E7-9221-4578-947B-8DB8C397A7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57F3595-7FB6-4944-8263-89E65057008E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="157">
   <si>
     <t>##var</t>
   </si>
@@ -83,22 +83,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>能量值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自定义属性1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自定义属性2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自定义属性3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Energy</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -111,15 +95,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CustomGauge01</t>
-  </si>
-  <si>
-    <t>CustomGauge02</t>
-  </si>
-  <si>
-    <t>CustomGauge03</t>
-  </si>
-  <si>
     <t>HP</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -176,13 +151,423 @@
   </si>
   <si>
     <t>仅首次命中触发</t>
+  </si>
+  <si>
+    <t>MaxHp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxEnergy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>喧响值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CritDmg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Impact</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PenRate</t>
+  </si>
+  <si>
+    <t>PenValue</t>
+  </si>
+  <si>
+    <t>Decibel</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DecibelGenRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnomalyMastery</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AnomalyProficiency</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PhysicalDmgBonus</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FireDmgBonus</t>
+  </si>
+  <si>
+    <t>IceDmgBonus</t>
+  </si>
+  <si>
+    <t>ElectricDmgBonus</t>
+  </si>
+  <si>
+    <t>EtherDmgBonus</t>
+  </si>
+  <si>
+    <t>PhysicalRes</t>
+  </si>
+  <si>
+    <t>FireRes</t>
+  </si>
+  <si>
+    <t>IceRes</t>
+  </si>
+  <si>
+    <t>ElectricRes</t>
+  </si>
+  <si>
+    <t>EtherRes</t>
+  </si>
+  <si>
+    <t>Anbi_Voltage</t>
+  </si>
+  <si>
+    <t>最大生命值</t>
+  </si>
+  <si>
+    <t>攻击力</t>
+  </si>
+  <si>
+    <t>防御力</t>
+  </si>
+  <si>
+    <t>冲击力</t>
+  </si>
+  <si>
+    <t>失衡易伤倍率</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击伤害</t>
+  </si>
+  <si>
+    <t>穿透率</t>
+  </si>
+  <si>
+    <t>穿透值</t>
+  </si>
+  <si>
+    <t>当前能量值</t>
+  </si>
+  <si>
+    <t>能量上限</t>
+  </si>
+  <si>
+    <t>能量自动回复 (点/秒)</t>
+  </si>
+  <si>
+    <t>能量获得效率 (%)</t>
+  </si>
+  <si>
+    <t>喧响值获取效率 (%)</t>
+  </si>
+  <si>
+    <t>异常掌控</t>
+  </si>
+  <si>
+    <t>异常精通</t>
+  </si>
+  <si>
+    <t>物理伤害加成</t>
+  </si>
+  <si>
+    <t>火属性伤害加成</t>
+  </si>
+  <si>
+    <t>冰属性伤害加成</t>
+  </si>
+  <si>
+    <t>电属性伤害加成</t>
+  </si>
+  <si>
+    <t>以太属性伤害加成</t>
+  </si>
+  <si>
+    <t>物理抗性</t>
+  </si>
+  <si>
+    <t>火属性抗性</t>
+  </si>
+  <si>
+    <t>冰属性抗性</t>
+  </si>
+  <si>
+    <t>电属性抗性</t>
+  </si>
+  <si>
+    <t>以太属性抗性</t>
+  </si>
+  <si>
+    <t>急冻充能</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电荷值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CompareOp</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Greater</t>
+  </si>
+  <si>
+    <t>LessEqual</t>
+  </si>
+  <si>
+    <t>Less</t>
+  </si>
+  <si>
+    <t>Equal</t>
+  </si>
+  <si>
+    <t>大于等于 &gt;=</t>
+  </si>
+  <si>
+    <t>大于 &gt;</t>
+  </si>
+  <si>
+    <t>小于等于 &lt;=</t>
+  </si>
+  <si>
+    <t>小于 &lt;</t>
+  </si>
+  <si>
+    <t>等于 ==</t>
+  </si>
+  <si>
+    <t>条件运算符</t>
+  </si>
+  <si>
+    <t>命中策略</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>影响类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CostType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>消耗计算类型</t>
+  </si>
+  <si>
+    <t>PercentMax</t>
+  </si>
+  <si>
+    <t>PercentCurrent</t>
+  </si>
+  <si>
+    <t>固定数值扣减</t>
+  </si>
+  <si>
+    <t>最大值百分比扣减</t>
+  </si>
+  <si>
+    <t>当前值百分比扣减</t>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF292929"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ellen_FlashFreeze</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>GreaterEqual</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FixedValue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>角色ID</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Anbi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Miyabi</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CharacterId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ATK</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DEF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>StunDmgMultiplier</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyRegen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EnergyGenRate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.ElementType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素属性</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Physical</t>
+  </si>
+  <si>
+    <t>Fire</t>
+  </si>
+  <si>
+    <t>Ice</t>
+  </si>
+  <si>
+    <t>Ether</t>
+  </si>
+  <si>
+    <t>物理</t>
+  </si>
+  <si>
+    <t>火</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>冰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以太</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>安比</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星见雅</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲乔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.CombatStyle</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战斗定位</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stun</t>
+  </si>
+  <si>
+    <t>Anomaly</t>
+  </si>
+  <si>
+    <t>Support</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>未指定</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强攻</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击破</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>支援</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>防护</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Electric</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Attack</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Allen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,6 +595,13 @@
       <color rgb="FF292929"/>
       <name val="Segoe UI"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
@@ -268,11 +660,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -549,7 +941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -557,10 +949,10 @@
     <col min="4" max="5" width="14.125" customWidth="1"/>
     <col min="6" max="6" width="9.375" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5" customWidth="1"/>
+    <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="15.125" customWidth="1"/>
+    <col min="10" max="10" width="18.625" customWidth="1"/>
+    <col min="11" max="11" width="31.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.2">
@@ -585,13 +977,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -651,149 +1043,741 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H5" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>3</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
         <v>30</v>
       </c>
-      <c r="J4">
-        <v>100</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H5" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
-        <v>200</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
-        <v>1000</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7">
-        <v>1100</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" s="3" t="s">
-        <v>29</v>
-      </c>
       <c r="J8">
-        <v>1200</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>23</v>
+        <v>2</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" s="3" t="s">
         <v>31</v>
       </c>
+      <c r="F9" s="3" t="s">
+        <v>103</v>
+      </c>
       <c r="H9" t="s">
         <v>32</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>41</v>
+      <c r="K9" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F10" s="3"/>
       <c r="H10" t="s">
         <v>33</v>
       </c>
       <c r="J10">
         <v>2</v>
       </c>
-      <c r="K10" s="5" t="s">
+      <c r="K10" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H12" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J12">
+        <v>10</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13">
+        <v>20</v>
+      </c>
+      <c r="K13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H14" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="J14">
+        <v>30</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15">
+        <v>40</v>
+      </c>
+      <c r="K15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16">
+        <v>50</v>
+      </c>
+      <c r="K16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H17" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="J17">
+        <v>60</v>
+      </c>
+      <c r="K17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H18" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J18">
+        <v>70</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H19" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19">
+        <v>80</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H20" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20">
+        <v>90</v>
+      </c>
+      <c r="K20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H21" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21">
+        <v>100</v>
+      </c>
+      <c r="K21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J22">
+        <v>110</v>
+      </c>
+      <c r="K22" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H23" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J11">
+      <c r="J23">
+        <v>120</v>
+      </c>
+      <c r="K23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="J24">
+        <v>130</v>
+      </c>
+      <c r="K24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F25" s="3"/>
+      <c r="H25" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J25">
+        <v>140</v>
+      </c>
+      <c r="K25" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="26" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F26" s="3"/>
+      <c r="H26" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J26">
+        <v>150</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H27" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27">
+        <v>160</v>
+      </c>
+      <c r="K27" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J28">
+        <v>170</v>
+      </c>
+      <c r="K28" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H29" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J29">
+        <v>180</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H30" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30">
+        <v>190</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="31" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H31" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J31">
+        <v>200</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="32" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H32" t="s">
+        <v>55</v>
+      </c>
+      <c r="J32">
+        <v>210</v>
+      </c>
+      <c r="K32" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H33" t="s">
+        <v>56</v>
+      </c>
+      <c r="J33">
+        <v>220</v>
+      </c>
+      <c r="K33" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H34" t="s">
+        <v>57</v>
+      </c>
+      <c r="J34">
+        <v>230</v>
+      </c>
+      <c r="K34" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H35" t="s">
+        <v>58</v>
+      </c>
+      <c r="J35">
+        <v>240</v>
+      </c>
+      <c r="K35" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H36" t="s">
+        <v>59</v>
+      </c>
+      <c r="J36">
+        <v>250</v>
+      </c>
+      <c r="K36" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H37" t="s">
+        <v>60</v>
+      </c>
+      <c r="J37">
+        <v>260</v>
+      </c>
+      <c r="K37" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H38" t="s">
+        <v>61</v>
+      </c>
+      <c r="J38">
+        <v>270</v>
+      </c>
+      <c r="K38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
+        <v>62</v>
+      </c>
+      <c r="J39">
+        <v>280</v>
+      </c>
+      <c r="K39" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H40" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="J40">
+        <v>2000</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
+        <v>63</v>
+      </c>
+      <c r="J41">
+        <v>2010</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B42" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F42" t="s">
+        <v>102</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
+        <v>93</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
+        <v>94</v>
+      </c>
+      <c r="J44">
+        <v>2</v>
+      </c>
+      <c r="K44" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
+        <v>95</v>
+      </c>
+      <c r="J45">
         <v>3</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" t="s">
-        <v>36</v>
-      </c>
-      <c r="J12">
+      <c r="K45" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
+        <v>96</v>
+      </c>
+      <c r="J46">
+        <v>4</v>
+      </c>
+      <c r="K46" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B47" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F47" t="s">
+        <v>107</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H48" t="s">
+        <v>108</v>
+      </c>
+      <c r="J48">
         <v>1</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H13" t="s">
-        <v>37</v>
-      </c>
-      <c r="J13">
+      <c r="K48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H49" t="s">
+        <v>109</v>
+      </c>
+      <c r="J49">
         <v>2</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" t="s">
-        <v>39</v>
-      </c>
-      <c r="J14">
+      <c r="K49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B50" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H51" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="J51">
+        <v>1001</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H52" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J52">
+        <v>1002</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H53" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J53">
+        <v>1003</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B54" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
+        <v>130</v>
+      </c>
+      <c r="J55">
         <v>1</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
-        <v>40</v>
-      </c>
-      <c r="J15">
+      <c r="K55" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H56" t="s">
+        <v>131</v>
+      </c>
+      <c r="J56">
         <v>2</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>47</v>
+      <c r="K56" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H57" t="s">
+        <v>132</v>
+      </c>
+      <c r="J57">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H58" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J58">
+        <v>4</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H59" t="s">
+        <v>133</v>
+      </c>
+      <c r="J59">
+        <v>5</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B60" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H61" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H62" t="s">
+        <v>144</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H63" t="s">
+        <v>145</v>
+      </c>
+      <c r="J63">
+        <v>3</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H64" t="s">
+        <v>146</v>
+      </c>
+      <c r="J64">
+        <v>4</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="8:11" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>147</v>
+      </c>
+      <c r="J65">
+        <v>5</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E57F3595-7FB6-4944-8263-89E65057008E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC8F50C-5E47-466E-A2F3-97419C5AC5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -503,10 +503,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>艾莲乔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>ZZZ.CombatStyle</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -559,7 +555,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Allen</t>
+    <t>Ellen</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾莲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1627,13 +1627,13 @@
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H53" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="J53">
         <v>1003</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
@@ -1688,7 +1688,7 @@
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H58" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J58">
         <v>4</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B60" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>143</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>113</v>
@@ -1722,62 +1722,62 @@
         <v>0</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H61" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="J61">
         <v>1</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H62" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J62">
         <v>2</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H63" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J63">
         <v>3</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H64" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J64">
         <v>4</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="65" spans="8:11" x14ac:dyDescent="0.2">
       <c r="H65" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="J65">
         <v>5</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC8F50C-5E47-466E-A2F3-97419C5AC5E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28F269F-9857-428F-91C7-FE3217968413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="174">
   <si>
     <t>##var</t>
   </si>
@@ -562,12 +562,80 @@
     <t>艾莲</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>Shake</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Light</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Heavy</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stay</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Launch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KnockDown</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击反馈类型</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZZZ.HitReactionType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不打断,无受击动作</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>原地打断</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击飞</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>击倒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不打断,原地抖动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>轻击击退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重击击退</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BaseResilience</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>基础抗打断等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -601,6 +669,13 @@
       <color rgb="FF292929"/>
       <name val="等线"/>
       <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF292929"/>
+      <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -647,7 +722,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -661,6 +736,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -941,13 +1022,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
     <col min="3" max="3" width="20.875" customWidth="1"/>
     <col min="4" max="5" width="14.125" customWidth="1"/>
-    <col min="6" max="6" width="9.375" customWidth="1"/>
+    <col min="6" max="6" width="12.375" customWidth="1"/>
     <col min="7" max="7" width="5" customWidth="1"/>
     <col min="8" max="8" width="22.625" customWidth="1"/>
     <col min="9" max="9" width="5.25" customWidth="1"/>
@@ -977,13 +1058,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1082,701 +1163,795 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>164</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="H7" t="s">
-        <v>29</v>
+        <v>163</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>37</v>
+        <v>0</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="J8">
+        <v>10</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9">
+        <v>20</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H10" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="J10">
         <v>30</v>
       </c>
-      <c r="J8">
-        <v>2</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F10" s="3"/>
-      <c r="H10" t="s">
-        <v>33</v>
-      </c>
-      <c r="J10">
-        <v>2</v>
-      </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="J11">
         <v>40</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>115</v>
+      <c r="K11" s="3" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H12" s="3" t="s">
-        <v>23</v>
+        <v>161</v>
       </c>
       <c r="J12">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>19</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="H13" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="J13">
+        <v>60</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F17" s="3"/>
+      <c r="H17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17">
+        <v>2</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J19">
+        <v>10</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J13">
+      <c r="J20">
         <v>20</v>
       </c>
-      <c r="K13" t="s">
+      <c r="K20" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H14" s="3" t="s">
+    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H21" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="J14">
+      <c r="J21">
         <v>30</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" s="3" t="s">
+    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H22" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="J15">
+      <c r="J22">
         <v>40</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H16" s="3" t="s">
+    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H23" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="J16">
+      <c r="J23">
         <v>50</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K23" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="17" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H17" s="3" t="s">
+    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H24" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J17">
+      <c r="J24">
         <v>60</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K24" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H18" s="3" t="s">
+    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H25" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J18">
+      <c r="J25">
         <v>70</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H19" s="3" t="s">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H26" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J19">
+      <c r="J26">
         <v>80</v>
       </c>
-      <c r="K19" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="20" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H20" t="s">
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H27" t="s">
         <v>47</v>
       </c>
-      <c r="J20">
+      <c r="J27">
         <v>90</v>
       </c>
-      <c r="K20" t="s">
+      <c r="K27" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H21" t="s">
+    <row r="28" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H28" t="s">
         <v>48</v>
       </c>
-      <c r="J21">
+      <c r="J28">
         <v>100</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K28" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="22" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H22" s="3" t="s">
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H29" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="J22">
+      <c r="J29">
         <v>110</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K29" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="23" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H23" s="3" t="s">
+    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H30" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="J23">
+      <c r="J30">
         <v>120</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K30" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="24" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H24" s="3" t="s">
+    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H31" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J24">
+      <c r="J31">
         <v>130</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K31" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="25" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F25" s="3"/>
-      <c r="H25" s="3" t="s">
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F32" s="3"/>
+      <c r="H32" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J25">
+      <c r="J32">
         <v>140</v>
       </c>
-      <c r="K25" t="s">
+      <c r="K32" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="F26" s="3"/>
-      <c r="H26" s="3" t="s">
+    <row r="33" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F33" s="3"/>
+      <c r="H33" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J26">
+      <c r="J33">
         <v>150</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="K33" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="27" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H27" s="3" t="s">
+    <row r="34" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H34" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="J27">
+      <c r="J34">
         <v>160</v>
       </c>
-      <c r="K27" t="s">
+      <c r="K34" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="28" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H28" s="3" t="s">
+    <row r="35" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H35" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="J28">
+      <c r="J35">
         <v>170</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H29" s="3" t="s">
+    <row r="36" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H36" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="J29">
+      <c r="J36">
         <v>180</v>
       </c>
-      <c r="K29" s="3" t="s">
+      <c r="K36" s="3" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="30" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H30" s="3" t="s">
+    <row r="37" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H37" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="J30">
+      <c r="J37">
         <v>190</v>
       </c>
-      <c r="K30" s="3" t="s">
+      <c r="K37" s="3" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H31" s="3" t="s">
+    <row r="38" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H38" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J31">
+      <c r="J38">
         <v>200</v>
       </c>
-      <c r="K31" s="3" t="s">
+      <c r="K38" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H32" t="s">
+    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H39" t="s">
         <v>55</v>
       </c>
-      <c r="J32">
+      <c r="J39">
         <v>210</v>
       </c>
-      <c r="K32" t="s">
+      <c r="K39" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H33" t="s">
+    <row r="40" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H40" t="s">
         <v>56</v>
       </c>
-      <c r="J33">
+      <c r="J40">
         <v>220</v>
       </c>
-      <c r="K33" t="s">
+      <c r="K40" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H34" t="s">
+    <row r="41" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H41" t="s">
         <v>57</v>
       </c>
-      <c r="J34">
+      <c r="J41">
         <v>230</v>
       </c>
-      <c r="K34" t="s">
+      <c r="K41" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H35" t="s">
+    <row r="42" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H42" t="s">
         <v>58</v>
       </c>
-      <c r="J35">
+      <c r="J42">
         <v>240</v>
       </c>
-      <c r="K35" t="s">
+      <c r="K42" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H36" t="s">
+    <row r="43" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H43" t="s">
         <v>59</v>
       </c>
-      <c r="J36">
+      <c r="J43">
         <v>250</v>
       </c>
-      <c r="K36" t="s">
+      <c r="K43" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H37" t="s">
+    <row r="44" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H44" t="s">
         <v>60</v>
       </c>
-      <c r="J37">
+      <c r="J44">
         <v>260</v>
       </c>
-      <c r="K37" t="s">
+      <c r="K44" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H38" t="s">
+    <row r="45" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H45" t="s">
         <v>61</v>
       </c>
-      <c r="J38">
+      <c r="J45">
         <v>270</v>
       </c>
-      <c r="K38" t="s">
+      <c r="K45" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H39" t="s">
+    <row r="46" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H46" t="s">
         <v>62</v>
       </c>
-      <c r="J39">
+      <c r="J46">
         <v>280</v>
       </c>
-      <c r="K39" t="s">
+      <c r="K46" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="40" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H40" s="3" t="s">
+    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H47" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J47">
+        <v>290</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="48" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H48" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J40">
+      <c r="J48">
         <v>2000</v>
       </c>
-      <c r="K40" s="3" t="s">
+      <c r="K48" s="3" t="s">
         <v>90</v>
-      </c>
-    </row>
-    <row r="41" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H41" t="s">
-        <v>63</v>
-      </c>
-      <c r="J41">
-        <v>2010</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B42" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="F42" t="s">
-        <v>102</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H43" t="s">
-        <v>93</v>
-      </c>
-      <c r="J43">
-        <v>1</v>
-      </c>
-      <c r="K43" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H44" t="s">
-        <v>94</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H45" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45">
-        <v>3</v>
-      </c>
-      <c r="K45" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H46" t="s">
-        <v>96</v>
-      </c>
-      <c r="J46">
-        <v>4</v>
-      </c>
-      <c r="K46" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B47" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="F47" t="s">
-        <v>107</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H48" t="s">
-        <v>108</v>
-      </c>
-      <c r="J48">
-        <v>1</v>
-      </c>
-      <c r="K48" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H49" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="J49">
-        <v>2</v>
-      </c>
-      <c r="K49" t="s">
-        <v>112</v>
+        <v>2010</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>119</v>
+        <v>92</v>
+      </c>
+      <c r="F50" t="s">
+        <v>102</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J50">
         <v>0</v>
       </c>
-      <c r="K50" s="3" t="s">
-        <v>114</v>
+      <c r="K50" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H51" s="3" t="s">
-        <v>120</v>
+      <c r="H51" t="s">
+        <v>93</v>
       </c>
       <c r="J51">
-        <v>1001</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>139</v>
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H52" s="3" t="s">
-        <v>121</v>
+      <c r="H52" t="s">
+        <v>94</v>
       </c>
       <c r="J52">
-        <v>1002</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>140</v>
+        <v>2</v>
+      </c>
+      <c r="K52" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H53" s="3" t="s">
-        <v>155</v>
+      <c r="H53" t="s">
+        <v>95</v>
       </c>
       <c r="J53">
-        <v>1003</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>156</v>
+        <v>3</v>
+      </c>
+      <c r="K53" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B54" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>113</v>
+      <c r="H54" t="s">
+        <v>96</v>
       </c>
       <c r="J54">
+        <v>4</v>
+      </c>
+      <c r="K54" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B55" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F55" t="s">
+        <v>107</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="J55">
         <v>0</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H55" t="s">
-        <v>130</v>
-      </c>
-      <c r="J55">
-        <v>1</v>
-      </c>
       <c r="K55" t="s">
-        <v>134</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H56" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="J56">
-        <v>2</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="K56" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H57" t="s">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="J57">
-        <v>3</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>136</v>
+        <v>2</v>
+      </c>
+      <c r="K57" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B58" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>119</v>
+      </c>
       <c r="H58" s="3" t="s">
-        <v>153</v>
+        <v>113</v>
       </c>
       <c r="J58">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H59" t="s">
-        <v>133</v>
+      <c r="H59" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="J59">
-        <v>5</v>
+        <v>1001</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B60" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>142</v>
-      </c>
       <c r="H60" s="3" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="J60">
-        <v>0</v>
+        <v>1002</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H61" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>1003</v>
       </c>
       <c r="K61" s="3" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
     </row>
     <row r="62" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H62" t="s">
-        <v>143</v>
+      <c r="B62" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>113</v>
       </c>
       <c r="J62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>149</v>
+        <v>114</v>
       </c>
     </row>
     <row r="63" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H63" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="J63">
-        <v>3</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>150</v>
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H64" t="s">
+        <v>131</v>
+      </c>
+      <c r="J64">
+        <v>2</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H65" t="s">
+        <v>132</v>
+      </c>
+      <c r="J65">
+        <v>3</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H66" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J66">
+        <v>4</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H67" t="s">
+        <v>133</v>
+      </c>
+      <c r="J67">
+        <v>5</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B68" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H69" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="J69">
+        <v>1</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H70" t="s">
+        <v>143</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="71" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H71" t="s">
+        <v>144</v>
+      </c>
+      <c r="J71">
+        <v>3</v>
+      </c>
+      <c r="K71" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="72" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H72" t="s">
         <v>145</v>
       </c>
-      <c r="J64">
+      <c r="J72">
         <v>4</v>
       </c>
-      <c r="K64" s="3" t="s">
+      <c r="K72" s="3" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="65" spans="8:11" x14ac:dyDescent="0.2">
-      <c r="H65" t="s">
+    <row r="73" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H73" t="s">
         <v>146</v>
       </c>
-      <c r="J65">
+      <c r="J73">
         <v>5</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="K73" s="3" t="s">
         <v>152</v>
       </c>
     </row>

--- a/Configs/Datas/__enums__.xlsx
+++ b/Configs/Datas/__enums__.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity\ZZZ\Configs\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B28F269F-9857-428F-91C7-FE3217968413}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82709D9B-8265-46DB-8179-BECD857A3F60}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="176">
   <si>
     <t>##var</t>
   </si>
@@ -628,6 +628,14 @@
   </si>
   <si>
     <t>基础抗打断等级</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Parried </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被格挡</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1022,7 +1030,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L74"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
@@ -1245,713 +1253,724 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="J14">
+        <v>70</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H14" t="s">
+      <c r="H15" t="s">
         <v>29</v>
       </c>
-      <c r="J14">
+      <c r="J15">
         <v>1</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="H15" t="s">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="H16" t="s">
         <v>30</v>
       </c>
-      <c r="J15">
+      <c r="J16">
         <v>2</v>
       </c>
-      <c r="K15" s="4" t="s">
+      <c r="K16" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B17" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F17" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="H16" t="s">
+      <c r="H17" t="s">
         <v>32</v>
       </c>
-      <c r="J16">
+      <c r="J17">
         <v>1</v>
       </c>
-      <c r="K16" s="4" t="s">
+      <c r="K17" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="F17" s="3"/>
-      <c r="H17" t="s">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F18" s="3"/>
+      <c r="H18" t="s">
         <v>33</v>
       </c>
-      <c r="J17">
+      <c r="J18">
         <v>2</v>
       </c>
-      <c r="K17" s="4" t="s">
+      <c r="K18" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="3" t="s">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="3" t="s">
+      <c r="H19" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J18">
+      <c r="J19">
         <v>0</v>
       </c>
-      <c r="K18" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H19" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J19">
-        <v>10</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H20" s="3" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="J20">
-        <v>20</v>
-      </c>
-      <c r="K20" t="s">
-        <v>64</v>
+        <v>10</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H21" s="3" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="J21">
-        <v>30</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>65</v>
+        <v>20</v>
+      </c>
+      <c r="K21" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H22" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="J22">
-        <v>40</v>
-      </c>
-      <c r="K22" t="s">
-        <v>66</v>
+        <v>30</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H23" s="3" t="s">
-        <v>46</v>
+        <v>124</v>
       </c>
       <c r="J23">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H24" s="3" t="s">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c r="J24">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="K24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H25" s="3" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="J25">
-        <v>70</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>69</v>
+        <v>60</v>
+      </c>
+      <c r="K25" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J26">
+        <v>70</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H27" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="J26">
+      <c r="J27">
         <v>80</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H27" t="s">
-        <v>47</v>
-      </c>
-      <c r="J27">
-        <v>90</v>
-      </c>
-      <c r="K27" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H28" t="s">
+        <v>47</v>
+      </c>
+      <c r="J28">
+        <v>90</v>
+      </c>
+      <c r="K28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H29" t="s">
         <v>48</v>
       </c>
-      <c r="J28">
+      <c r="J29">
         <v>100</v>
       </c>
-      <c r="K28" t="s">
+      <c r="K29" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J29">
-        <v>110</v>
-      </c>
-      <c r="K29" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H30" s="3" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="J30">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="K30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H31" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J31">
+        <v>120</v>
+      </c>
+      <c r="K31" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H32" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="J31">
+      <c r="J32">
         <v>130</v>
       </c>
-      <c r="K31" t="s">
+      <c r="K32" t="s">
         <v>75</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="F32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J32">
-        <v>140</v>
-      </c>
-      <c r="K32" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="33" spans="6:11" x14ac:dyDescent="0.2">
       <c r="F33" s="3"/>
       <c r="H33" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="J33">
+        <v>140</v>
+      </c>
+      <c r="K33" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="34" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="F34" s="3"/>
+      <c r="H34" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J33">
+      <c r="J34">
         <v>150</v>
       </c>
-      <c r="K33" s="3" t="s">
+      <c r="K34" s="3" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="34" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H34" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="J34">
-        <v>160</v>
-      </c>
-      <c r="K34" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="35" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H35" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J35">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="K35" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="36" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H36" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J36">
-        <v>180</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>79</v>
+        <v>170</v>
+      </c>
+      <c r="K36" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H37" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J37">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="J38">
+        <v>190</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H39" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="J38">
+      <c r="J39">
         <v>200</v>
       </c>
-      <c r="K38" s="3" t="s">
+      <c r="K39" s="3" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="39" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H39" t="s">
-        <v>55</v>
-      </c>
-      <c r="J39">
-        <v>210</v>
-      </c>
-      <c r="K39" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="40" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H40" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="J40">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="K40" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H41" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J41">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="K41" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H42" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J42">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="K42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H43" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J43">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="K43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="44" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H44" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J44">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="K44" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J45">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="K45" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="46" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H46" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46">
+        <v>270</v>
+      </c>
+      <c r="K46" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
+      <c r="H47" t="s">
         <v>62</v>
       </c>
-      <c r="J46">
+      <c r="J47">
         <v>280</v>
       </c>
-      <c r="K46" t="s">
+      <c r="K47" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="6:11" x14ac:dyDescent="0.2">
-      <c r="H47" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="J47">
-        <v>290</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="48" spans="6:11" x14ac:dyDescent="0.2">
       <c r="H48" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="J48">
+        <v>290</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H49" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J48">
+      <c r="J49">
         <v>2000</v>
       </c>
-      <c r="K48" s="3" t="s">
+      <c r="K49" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H49" t="s">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H50" t="s">
         <v>63</v>
       </c>
-      <c r="J49">
+      <c r="J50">
         <v>2010</v>
       </c>
-      <c r="K49" s="3" t="s">
+      <c r="K50" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B50" s="3" t="s">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B51" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F50" t="s">
+      <c r="F51" t="s">
         <v>102</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="J50">
+      <c r="J51">
         <v>0</v>
       </c>
-      <c r="K50" t="s">
+      <c r="K51" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H51" t="s">
-        <v>93</v>
-      </c>
-      <c r="J51">
-        <v>1</v>
-      </c>
-      <c r="K51" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H52" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="J52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H53" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="J53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="54" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H54" t="s">
+        <v>95</v>
+      </c>
+      <c r="J54">
+        <v>3</v>
+      </c>
+      <c r="K54" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H55" t="s">
         <v>96</v>
       </c>
-      <c r="J54">
+      <c r="J55">
         <v>4</v>
       </c>
-      <c r="K54" t="s">
+      <c r="K55" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="55" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B55" s="3" t="s">
+    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B56" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F56" t="s">
         <v>107</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J55">
+      <c r="J56">
         <v>0</v>
       </c>
-      <c r="K55" t="s">
+      <c r="K56" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H56" t="s">
-        <v>108</v>
-      </c>
-      <c r="J56">
-        <v>1</v>
-      </c>
-      <c r="K56" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H57" t="s">
+        <v>108</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H58" t="s">
         <v>109</v>
       </c>
-      <c r="J57">
+      <c r="J58">
         <v>2</v>
       </c>
-      <c r="K57" t="s">
+      <c r="K58" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B58" s="3" t="s">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B59" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="H59" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J58">
+      <c r="J59">
         <v>0</v>
       </c>
-      <c r="K58" s="3" t="s">
+      <c r="K59" s="3" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H59" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="J59">
-        <v>1001</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H60" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J60">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="K60" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H61" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="J61">
+        <v>1002</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H62" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="J61">
+      <c r="J62">
         <v>1003</v>
       </c>
-      <c r="K61" s="3" t="s">
+      <c r="K62" s="3" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B62" s="3" t="s">
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B63" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J62">
+      <c r="J63">
         <v>0</v>
       </c>
-      <c r="K62" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>114</v>
-      </c>
-    </row>
-    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H63" t="s">
-        <v>130</v>
-      </c>
-      <c r="J63">
-        <v>1</v>
-      </c>
-      <c r="K63" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="64" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H64" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="J64">
-        <v>2</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>135</v>
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H65" t="s">
+        <v>131</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H66" t="s">
         <v>132</v>
       </c>
-      <c r="J65">
+      <c r="J66">
         <v>3</v>
       </c>
-      <c r="K65" s="3" t="s">
+      <c r="K66" s="3" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="66" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H66" s="3" t="s">
+    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H67" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="J66">
+      <c r="J67">
         <v>4</v>
       </c>
-      <c r="K66" s="3" t="s">
+      <c r="K67" s="3" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H67" t="s">
+    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H68" t="s">
         <v>133</v>
       </c>
-      <c r="J67">
+      <c r="J68">
         <v>5</v>
       </c>
-      <c r="K67" s="3" t="s">
+      <c r="K68" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="68" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B68" s="3" t="s">
+    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B69" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="F69" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="J68">
+      <c r="J69">
         <v>0</v>
       </c>
-      <c r="K68" s="3" t="s">
+      <c r="K69" s="3" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="69" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H69" s="3" t="s">
+    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H70" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J69">
+      <c r="J70">
         <v>1</v>
       </c>
-      <c r="K69" s="3" t="s">
+      <c r="K70" s="3" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="70" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="H70" t="s">
-        <v>143</v>
-      </c>
-      <c r="J70">
-        <v>2</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="71" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H71" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="72" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="2:11" x14ac:dyDescent="0.2">
       <c r="H73" t="s">
+        <v>145</v>
+      </c>
+      <c r="J73">
+        <v>4</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="H74" t="s">
         <v>146</v>
       </c>
-      <c r="J73">
+      <c r="J74">
         <v>5</v>
       </c>
-      <c r="K73" s="3" t="s">
+      <c r="K74" s="3" t="s">
         <v>152</v>
       </c>
     </row>
